--- a/output/2026-09-07_02_Slovenia_Goriska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-07_02_Slovenia_Goriska_Depolverazione_Trattamento_aria.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Produttore/distributore diretto di impianti industriali di depolverazione/aspirazione per fonderie (portata 0.5-4 t/h) sabbiatrici filtri FVL/FVS ingegneria di processo; esistenza e attività confermate (living.si)</t>
+          <t>Produttore/distributore diretto di impianti industriali di depolverazione/aspirazione per fonderie (portata 0.5-4 t/h) sabbiatrici filtri FVL/FVS ingegneria di processo; esistenza e attività confermate (living.si) [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -548,7 +548,6 @@
           <t>KOVENT Kovinarstvo Jurij Ušaj s.p.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Nova Gorica - Kromberk (Goriška)</t>
